--- a/gestao_projetos/execucao_financeira/execucao_financeira.xlsx
+++ b/gestao_projetos/execucao_financeira/execucao_financeira.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ARGUS\gestao_projetos\execucao_financeira\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2328D631-673F-45C6-B1B7-68DDC1221245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A55C569-FA39-4D96-8A6F-52A7E5359313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49823ED3-3B2F-469D-97DF-36A3ABB00E6B}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1644,7 +1644,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9DB36DD7-534E-4BAC-8DEA-04C59BA20F0E}" name="Tabela dinâmica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9DB36DD7-534E-4BAC-8DEA-04C59BA20F0E}" name="Tabela dinâmica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="ascending" defaultSubtotal="0">
@@ -2127,6 +2127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F049E5-0281-4D5D-A75B-91688D40DD5E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2274,7 +2275,7 @@
         <v>-2750</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46234</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v>184.68</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>46234</v>
       </c>
@@ -2340,7 +2341,7 @@
         <v>-1.34</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>46234</v>
       </c>
@@ -2373,7 +2374,7 @@
         <v>-10.92</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>46265</v>
       </c>
@@ -2406,7 +2407,7 @@
         <v>154.41</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>46265</v>
       </c>
@@ -2439,7 +2440,7 @@
         <v>-6.32</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>46286</v>
       </c>
@@ -2472,7 +2473,7 @@
         <v>88.34</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>46286</v>
       </c>
@@ -2505,7 +2506,7 @@
         <v>-12.34</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>46219</v>
       </c>
@@ -2538,7 +2539,7 @@
         <v>-2800</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>46239</v>
       </c>
@@ -2571,7 +2572,7 @@
         <v>-2800</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>46273</v>
       </c>
@@ -2670,7 +2671,7 @@
         <v>-128.57</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>46205</v>
       </c>
@@ -2703,7 +2704,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>46213</v>
       </c>
@@ -2736,7 +2737,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>46238</v>
       </c>
@@ -2769,7 +2770,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>46267</v>
       </c>
@@ -2802,7 +2803,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>46234</v>
       </c>
@@ -2835,7 +2836,7 @@
         <v>986.69</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>46234</v>
       </c>
@@ -2868,7 +2869,7 @@
         <v>-1.77</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>46234</v>
       </c>
@@ -2901,7 +2902,7 @@
         <v>-21.31</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>46265</v>
       </c>
@@ -2934,7 +2935,7 @@
         <v>795.84</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>46265</v>
       </c>
@@ -2967,7 +2968,7 @@
         <v>-117.23</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>46265</v>
       </c>
@@ -3000,7 +3001,7 @@
         <v>-20.95</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>46286</v>
       </c>
@@ -3033,7 +3034,7 @@
         <v>249.61</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>46286</v>
       </c>
@@ -3099,7 +3100,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>46219</v>
       </c>
@@ -3132,7 +3133,7 @@
         <v>-12000</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>46239</v>
       </c>
@@ -3165,7 +3166,7 @@
         <v>-12000</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>46239</v>
       </c>
@@ -3198,7 +3199,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>46239</v>
       </c>
@@ -3231,7 +3232,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>46239</v>
       </c>
@@ -3264,7 +3265,7 @@
         <v>-7000</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>46239</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>46239</v>
       </c>
@@ -3330,7 +3331,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>46239</v>
       </c>
@@ -3363,7 +3364,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>46239</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>46239</v>
       </c>
@@ -3429,7 +3430,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>46239</v>
       </c>
@@ -3462,7 +3463,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>46239</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>46251</v>
       </c>
@@ -3528,7 +3529,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>46251</v>
       </c>
@@ -3561,7 +3562,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>46251</v>
       </c>
@@ -3594,7 +3595,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>46251</v>
       </c>
@@ -3627,7 +3628,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>46268</v>
       </c>
@@ -3660,7 +3661,7 @@
         <v>-12000</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46273</v>
       </c>
@@ -3693,7 +3694,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>46273</v>
       </c>
@@ -3726,7 +3727,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>46273</v>
       </c>
@@ -3759,7 +3760,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>46273</v>
       </c>
@@ -3792,7 +3793,7 @@
         <v>-7000</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>46273</v>
       </c>
@@ -3825,7 +3826,7 @@
         <v>-7000</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>46273</v>
       </c>
@@ -3858,7 +3859,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>46273</v>
       </c>
@@ -3891,7 +3892,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>46274</v>
       </c>
@@ -3924,7 +3925,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>46274</v>
       </c>
@@ -3957,7 +3958,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>46220</v>
       </c>
@@ -3990,7 +3991,7 @@
         <v>-3.16</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>46238</v>
       </c>
@@ -4023,7 +4024,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>46252</v>
       </c>
@@ -4056,7 +4057,7 @@
         <v>-12.64</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>46240</v>
       </c>
@@ -4089,7 +4090,7 @@
         <v>-28.44</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>46267</v>
       </c>
@@ -4122,7 +4123,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>46269</v>
       </c>
@@ -4155,7 +4156,7 @@
         <v>-3.16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>46276</v>
       </c>
@@ -4188,7 +4189,7 @@
         <v>-6.32</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>46274</v>
       </c>
@@ -4221,7 +4222,7 @@
         <v>-18.96</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>46203</v>
       </c>
@@ -4254,7 +4255,7 @@
         <v>334.52</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>46234</v>
       </c>
@@ -4287,7 +4288,7 @@
         <v>972.5</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>46234</v>
       </c>
@@ -4320,7 +4321,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>46234</v>
       </c>
@@ -4353,7 +4354,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>46265</v>
       </c>
@@ -4386,7 +4387,7 @@
         <v>859.45</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>46265</v>
       </c>
@@ -4419,7 +4420,7 @@
         <v>-14.42</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>46286</v>
       </c>
@@ -4452,7 +4453,7 @@
         <v>535.78</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>46286</v>
       </c>
@@ -4518,7 +4519,7 @@
         <v>103000</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>46239</v>
       </c>
@@ -4551,7 +4552,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>46251</v>
       </c>
@@ -4584,7 +4585,7 @@
         <v>-2125</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>46273</v>
       </c>
@@ -4617,7 +4618,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>46273</v>
       </c>
@@ -4650,7 +4651,7 @@
         <v>-2000</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>46274</v>
       </c>
@@ -4683,7 +4684,7 @@
         <v>-2125</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>46205</v>
       </c>
@@ -4716,7 +4717,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>46238</v>
       </c>
@@ -4749,7 +4750,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>46240</v>
       </c>
@@ -4782,7 +4783,7 @@
         <v>-3.16</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>46252</v>
       </c>
@@ -4815,7 +4816,7 @@
         <v>-3.16</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>46267</v>
       </c>
@@ -4848,7 +4849,7 @@
         <v>-34.5</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>46276</v>
       </c>
@@ -4881,7 +4882,7 @@
         <v>-3.16</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>46274</v>
       </c>
@@ -4927,7 +4928,14 @@
       <c r="J85" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J84" xr:uid="{E3F049E5-0281-4D5D-A75B-91688D40DD5E}"/>
+  <autoFilter ref="A1:J84" xr:uid="{E3F049E5-0281-4D5D-A75B-91688D40DD5E}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Entrada de Receita"/>
+        <filter val="Transferência entre Projetos"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/gestao_projetos/execucao_financeira/execucao_financeira.xlsx
+++ b/gestao_projetos/execucao_financeira/execucao_financeira.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ARGUS\gestao_projetos\execucao_financeira\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A55C569-FA39-4D96-8A6F-52A7E5359313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D87D72-B451-4084-9CB3-0DF0561CB703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49823ED3-3B2F-469D-97DF-36A3ABB00E6B}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1644,7 +1644,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9DB36DD7-534E-4BAC-8DEA-04C59BA20F0E}" name="Tabela dinâmica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9DB36DD7-534E-4BAC-8DEA-04C59BA20F0E}" name="Tabela dinâmica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="ascending" defaultSubtotal="0">
@@ -2176,7 +2176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46204</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>27500</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>46210</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>-1375</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>46213</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>-12.34</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>46219</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>-2800</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>46239</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>-2800</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>46273</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>-2800</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>46254</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>-128.58000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>46281</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>-200.93</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>46210</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>-32.07</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>46189</v>
       </c>
@@ -4929,10 +4929,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J84" xr:uid="{E3F049E5-0281-4D5D-A75B-91688D40DD5E}">
-    <filterColumn colId="7">
+    <filterColumn colId="8">
       <filters>
-        <filter val="Entrada de Receita"/>
-        <filter val="Transferência entre Projetos"/>
+        <filter val="Pagamento bolsa para Geziel Sena Colares, 83403876268, referente à parcela 01/08."/>
+        <filter val="Pagamento bolsa para Geziel Sena Colares, 83403876268, referente à parcela 02/08."/>
+        <filter val="Pagamento bolsa para Geziel Sena Colares, 83403876268, referente à parcela 03/08."/>
       </filters>
     </filterColumn>
   </autoFilter>
